--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>54385380</v>
+        <v>59771.17</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>36117452</v>
+        <v>39694.17</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33320000</v>
+        <v>36619.68</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29110899.79</v>
+        <v>31993.75</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18446218</v>
+        <v>20272.95</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>29951157.6</v>
+        <v>32917.22</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>49568039.85</v>
+        <v>54476.77</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21646098.81</v>
+        <v>23789.71</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33320000</v>
+        <v>36619.68</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33320000</v>
+        <v>36619.68</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>39949252</v>
+        <v>43905.43</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32387040</v>
+        <v>35594.33</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23390999.38</v>
+        <v>25707.41</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37569110.39</v>
+        <v>41289.58</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21409287.62</v>
+        <v>23529.45</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>43964802.28</v>
+        <v>48318.64</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17180999.85</v>
+        <v>18882.44</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>22310998.22</v>
+        <v>24520.46</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9790200.210000001</v>
+        <v>10759.72</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>21885050.81</v>
+        <v>24052.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>93355500</v>
+        <v>102600.5</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12286909.46</v>
+        <v>13503.68</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37573900.14</v>
+        <v>41294.85</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>30928100</v>
+        <v>33990.91</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11615699.48</v>
+        <v>12766</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>18945990</v>
+        <v>20822.21</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>34366188.5</v>
+        <v>37769.48</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>34743779.07</v>
+        <v>38184.46</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>35042797.51</v>
+        <v>38513.09</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>56665753.2</v>
+        <v>62277.37</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17999999.5</v>
+        <v>19782.54</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25181999.36</v>
+        <v>27675.77</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41666799.23</v>
+        <v>45793.07</v>
       </c>
     </row>
     <row r="35">
@@ -2582,11 +2582,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>23650900.14</v>
+        <v>25993.05</v>
       </c>
     </row>
     <row r="36">
@@ -2643,11 +2643,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>32387040</v>
+        <v>35594.33</v>
       </c>
     </row>
     <row r="37">
@@ -2704,11 +2704,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>34821000.55</v>
+        <v>38269.33</v>
       </c>
     </row>
     <row r="38">
@@ -2765,11 +2765,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>24397380</v>
+        <v>26813.45</v>
       </c>
     </row>
     <row r="39">
@@ -2826,11 +2826,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>24375831.48</v>
+        <v>26789.77</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>69736468.06</v>
+        <v>76642.48</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35042786.8</v>
+        <v>38513.08</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>48601861</v>
+        <v>53414.91</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>22310999.41</v>
+        <v>24520.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>69039103.06999999</v>
+        <v>75876.05</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>22376760</v>
+        <v>24592.73</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>20282287.41</v>
+        <v>22290.84</v>
       </c>
     </row>
     <row r="47">
@@ -3314,11 +3314,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>16054287.62</v>
+        <v>17644.15</v>
       </c>
     </row>
     <row r="48">
@@ -3375,11 +3375,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>21885052</v>
+        <v>24052.33</v>
       </c>
     </row>
     <row r="49">
@@ -3436,11 +3436,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>27796972</v>
+        <v>30549.71</v>
       </c>
     </row>
     <row r="50">
@@ -3497,11 +3497,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>33201000</v>
+        <v>36488.9</v>
       </c>
     </row>
     <row r="51">
@@ -3558,11 +3558,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>35010990</v>
+        <v>38478.13</v>
       </c>
     </row>
     <row r="52">
@@ -3619,11 +3619,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20997431</v>
+        <v>23076.81</v>
       </c>
     </row>
     <row r="53">
@@ -3680,11 +3680,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>39951000.11</v>
+        <v>43907.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,11 +3741,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>38748780</v>
+        <v>42586.07</v>
       </c>
     </row>
     <row r="55">
@@ -3802,11 +3802,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23015787.62</v>
+        <v>25295.04</v>
       </c>
     </row>
     <row r="56">
@@ -3863,11 +3863,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>61475611.82</v>
+        <v>67563.55</v>
       </c>
     </row>
     <row r="57">
@@ -3924,11 +3924,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>19412731.8</v>
+        <v>21335.18</v>
       </c>
     </row>
     <row r="58">
@@ -3985,11 +3985,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>28791000.42</v>
+        <v>31642.18</v>
       </c>
     </row>
     <row r="59">
@@ -4046,11 +4046,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12421930.43</v>
+        <v>13652.08</v>
       </c>
     </row>
     <row r="60">
@@ -4107,11 +4107,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>25191000.52</v>
+        <v>27685.67</v>
       </c>
     </row>
     <row r="61">
@@ -4168,11 +4168,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>20664210.77</v>
+        <v>22710.59</v>
       </c>
     </row>
     <row r="62">
@@ -4229,11 +4229,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>47690999.3</v>
+        <v>52413.84</v>
       </c>
     </row>
   </sheetData>
